--- a/src/nodes/P/compressor_stage_parameters.xlsx
+++ b/src/nodes/P/compressor_stage_parameters.xlsx
@@ -656,7 +656,7 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>140.51045823300962</v>
@@ -668,13 +668,13 @@
         <v>54.427938704640262</v>
       </c>
       <c r="G3">
-        <v>39.745762965652766</v>
+        <v>111.28813630382774</v>
       </c>
       <c r="H3">
         <v>3.953967464922127</v>
       </c>
       <c r="I3">
-        <v>2.4944340338927775</v>
+        <v>-2.3234164164668654</v>
       </c>
       <c r="J3">
         <v>0.18031787224058937</v>
@@ -686,31 +686,31 @@
         <v>74.709159537502785</v>
       </c>
       <c r="M3">
-        <v>15.861884919908942</v>
+        <v>25.471093906237609</v>
       </c>
       <c r="N3">
         <v>8.38434698469268</v>
       </c>
       <c r="O3">
-        <v>2.8401218641543373</v>
+        <v>7.6314804001233609</v>
       </c>
       <c r="P3">
         <v>37.354579768751393</v>
       </c>
       <c r="Q3">
-        <v>7.9309424599544709</v>
+        <v>12.735546953118805</v>
       </c>
       <c r="R3">
         <v>85.870831095646608</v>
       </c>
       <c r="S3">
-        <v>44.902075857276074</v>
+        <v>44.888829900080765</v>
       </c>
       <c r="T3">
         <v>115.79020180608937</v>
       </c>
       <c r="U3">
-        <v>431.76284883469441</v>
+        <v>270.2382527824422</v>
       </c>
       <c r="V3">
         <v>1.1407876045249155</v>
@@ -722,22 +722,22 @@
         <v>0.32767908419821812</v>
       </c>
       <c r="Y3">
-        <v>0.55430417103100249</v>
+        <v>0.70013496377231055</v>
       </c>
       <c r="Z3">
         <v>0.060410988057318517</v>
       </c>
       <c r="AA3">
-        <v>0.1857629491801743</v>
+        <v>0.10994635677701724</v>
       </c>
       <c r="AB3">
         <v>25.284183429755018</v>
       </c>
       <c r="AC3">
-        <v>3.3472753690407782</v>
+        <v>6.36383861602787</v>
       </c>
       <c r="AD3">
-        <v>57.04255978758308</v>
+        <v>73.492976393686448</v>
       </c>
     </row>
   </sheetData>
@@ -1062,7 +1062,7 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>165.53623608479259</v>
@@ -1074,13 +1074,13 @@
         <v>99.887549538806027</v>
       </c>
       <c r="G3">
-        <v>67.071422444730246</v>
+        <v>187.79998284524467</v>
       </c>
       <c r="H3">
         <v>1.6430647975922725</v>
       </c>
       <c r="I3">
-        <v>-0.031556739564154723</v>
+        <v>-3.2255559784157697</v>
       </c>
       <c r="J3">
         <v>0.33687146088590081</v>
@@ -1092,31 +1092,31 @@
         <v>15.087565624308507</v>
       </c>
       <c r="M3">
-        <v>15.699017747375788</v>
+        <v>24.350363058414928</v>
       </c>
       <c r="N3">
         <v>3.9481399024344097</v>
       </c>
       <c r="O3">
-        <v>3.420577387389967</v>
+        <v>8.8779234595774934</v>
       </c>
       <c r="P3">
         <v>7.5437828121542534</v>
       </c>
       <c r="Q3">
-        <v>7.8495088736878937</v>
+        <v>12.175181529207464</v>
       </c>
       <c r="R3">
         <v>32.968626647329764</v>
       </c>
       <c r="S3">
-        <v>46.990204243316128</v>
+        <v>48.121877659984087</v>
       </c>
       <c r="T3">
         <v>630.45201646512692</v>
       </c>
       <c r="U3">
-        <v>488.00850033540223</v>
+        <v>316.01550709754486</v>
       </c>
       <c r="V3">
         <v>0.89552238805970152</v>
@@ -1128,22 +1128,22 @@
         <v>0.52300000029597726</v>
       </c>
       <c r="Y3">
-        <v>0.36930688042793924</v>
+        <v>0.51881397320630085</v>
       </c>
       <c r="Z3">
         <v>0.11797979012784425</v>
       </c>
       <c r="AA3">
-        <v>0.062154000733578664</v>
+        <v>0.037929002640866009</v>
       </c>
       <c r="AB3">
         <v>8.47244299633755</v>
       </c>
       <c r="AC3">
-        <v>9.6961101016688325</v>
+        <v>16.505930146715617</v>
       </c>
       <c r="AD3">
-        <v>77.625779347882158</v>
+        <v>79.695539943115975</v>
       </c>
     </row>
   </sheetData>
@@ -1468,7 +1468,7 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D3">
         <v>182.66359570291252</v>
@@ -1480,13 +1480,13 @@
         <v>130.32675181840261</v>
       </c>
       <c r="G3">
-        <v>86.108746737158882</v>
+        <v>241.10449086404483</v>
       </c>
       <c r="H3">
         <v>1.0039543523158638</v>
       </c>
       <c r="I3">
-        <v>-0.84889558898739115</v>
+        <v>-3.5174627103526395</v>
       </c>
       <c r="J3">
         <v>0.37086234886233349</v>
@@ -1498,31 +1498,31 @@
         <v>1.1255486896717539</v>
       </c>
       <c r="M3">
-        <v>15.606107937915663</v>
+        <v>24.119562231060829</v>
       </c>
       <c r="N3">
         <v>0.35258823410251272</v>
       </c>
       <c r="O3">
-        <v>3.6849506974369852</v>
+        <v>9.5298378692169035</v>
       </c>
       <c r="P3">
         <v>0.562774344835877</v>
       </c>
       <c r="Q3">
-        <v>7.8030539689578315</v>
+        <v>12.059781115530415</v>
       </c>
       <c r="R3">
         <v>19.358639458099908</v>
       </c>
       <c r="S3">
-        <v>48.750482037067343</v>
+        <v>50.33864206227468</v>
       </c>
       <c r="T3">
         <v>9298.5949767388211</v>
       </c>
       <c r="U3">
-        <v>526.553231382303</v>
+        <v>342.16504331583866</v>
       </c>
       <c r="V3">
         <v>0.79255925137563821</v>
@@ -1534,22 +1534,22 @@
         <v>0.37359583653454487</v>
       </c>
       <c r="Y3">
-        <v>0.26626599295206171</v>
+        <v>0.40505635206665619</v>
       </c>
       <c r="Z3">
         <v>0.10383720771609799</v>
       </c>
       <c r="AA3">
-        <v>0.036471830377950917</v>
+        <v>0.020614899180637514</v>
       </c>
       <c r="AB3">
         <v>1.7645915651984336</v>
       </c>
       <c r="AC3">
-        <v>15.434428083305257</v>
+        <v>28.019204644275668</v>
       </c>
       <c r="AD3">
-        <v>39.014570332747688</v>
+        <v>39.933900402395139</v>
       </c>
     </row>
   </sheetData>
